--- a/fil-c-x64/Scattered unsuccessful looukp.xlsx
+++ b/fil-c-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>10.4541</v>
+        <v>10.4502</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5222</v>
+        <v>10.5161</v>
       </c>
       <c r="D2" t="n">
-        <v>29.352</v>
+        <v>28.7257</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5963</v>
+        <v>12.6206</v>
       </c>
       <c r="F2" t="n">
-        <v>13.0754</v>
+        <v>13.0627</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>10.849</v>
+        <v>10.8303</v>
       </c>
       <c r="C3" t="n">
-        <v>10.9587</v>
+        <v>10.9548</v>
       </c>
       <c r="D3" t="n">
-        <v>29.9124</v>
+        <v>29.8852</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6907</v>
+        <v>12.7215</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1716</v>
+        <v>13.1667</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>11.3574</v>
+        <v>11.3498</v>
       </c>
       <c r="C4" t="n">
-        <v>11.3947</v>
+        <v>11.3877</v>
       </c>
       <c r="D4" t="n">
-        <v>30.5984</v>
+        <v>30.5922</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9177</v>
+        <v>12.9107</v>
       </c>
       <c r="F4" t="n">
-        <v>13.3897</v>
+        <v>13.3732</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>12.1885</v>
+        <v>12.1813</v>
       </c>
       <c r="C5" t="n">
-        <v>12.133</v>
+        <v>12.1543</v>
       </c>
       <c r="D5" t="n">
-        <v>30.857</v>
+        <v>31.3802</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2649</v>
+        <v>13.3553</v>
       </c>
       <c r="F5" t="n">
-        <v>13.751</v>
+        <v>13.7312</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.1668</v>
+        <v>13.0734</v>
       </c>
       <c r="C6" t="n">
-        <v>13.5426</v>
+        <v>13.4736</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4885</v>
+        <v>32.2817</v>
       </c>
       <c r="E6" t="n">
-        <v>13.8456</v>
+        <v>13.8587</v>
       </c>
       <c r="F6" t="n">
-        <v>14.3491</v>
+        <v>14.3536</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>14.9202</v>
+        <v>14.986</v>
       </c>
       <c r="C7" t="n">
-        <v>15.2771</v>
+        <v>15.1138</v>
       </c>
       <c r="D7" t="n">
-        <v>27.0348</v>
+        <v>26.5416</v>
       </c>
       <c r="E7" t="n">
-        <v>15.0512</v>
+        <v>15.0218</v>
       </c>
       <c r="F7" t="n">
-        <v>15.5654</v>
+        <v>15.5732</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>17.8012</v>
+        <v>17.7953</v>
       </c>
       <c r="C8" t="n">
-        <v>18.0218</v>
+        <v>18.0293</v>
       </c>
       <c r="D8" t="n">
-        <v>27.6938</v>
+        <v>27.6947</v>
       </c>
       <c r="E8" t="n">
-        <v>17.1181</v>
+        <v>17.0836</v>
       </c>
       <c r="F8" t="n">
-        <v>17.6986</v>
+        <v>17.657</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.9179</v>
+        <v>21.6627</v>
       </c>
       <c r="C9" t="n">
-        <v>22.6482</v>
+        <v>22.3914</v>
       </c>
       <c r="D9" t="n">
-        <v>28.2739</v>
+        <v>28.3088</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2495</v>
+        <v>12.2502</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6455</v>
+        <v>12.6311</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>9.74765</v>
+        <v>9.746359999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>9.875679999999999</v>
+        <v>9.90607</v>
       </c>
       <c r="D10" t="n">
-        <v>29.0902</v>
+        <v>29.0908</v>
       </c>
       <c r="E10" t="n">
-        <v>12.284</v>
+        <v>12.2689</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6523</v>
+        <v>12.6546</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>9.82597</v>
+        <v>9.81761</v>
       </c>
       <c r="C11" t="n">
-        <v>9.973929999999999</v>
+        <v>9.96386</v>
       </c>
       <c r="D11" t="n">
-        <v>30.0746</v>
+        <v>29.6832</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3303</v>
+        <v>12.2997</v>
       </c>
       <c r="F11" t="n">
-        <v>12.6802</v>
+        <v>12.6842</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>9.8881</v>
+        <v>9.875629999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>10.073</v>
+        <v>10.048</v>
       </c>
       <c r="D12" t="n">
-        <v>29.7602</v>
+        <v>29.8813</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3584</v>
+        <v>12.3768</v>
       </c>
       <c r="F12" t="n">
-        <v>12.7679</v>
+        <v>12.7607</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>9.95166</v>
+        <v>9.940720000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>10.2203</v>
+        <v>10.1716</v>
       </c>
       <c r="D13" t="n">
-        <v>30.8485</v>
+        <v>30.4044</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4038</v>
+        <v>12.3949</v>
       </c>
       <c r="F13" t="n">
-        <v>12.82</v>
+        <v>12.7846</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>10.1117</v>
+        <v>10.1036</v>
       </c>
       <c r="C14" t="n">
-        <v>10.3818</v>
+        <v>10.3433</v>
       </c>
       <c r="D14" t="n">
-        <v>31.1393</v>
+        <v>31.6501</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4686</v>
+        <v>12.4843</v>
       </c>
       <c r="F14" t="n">
-        <v>12.877</v>
+        <v>12.863</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>10.2586</v>
+        <v>10.2452</v>
       </c>
       <c r="C15" t="n">
-        <v>10.619</v>
+        <v>10.5688</v>
       </c>
       <c r="D15" t="n">
-        <v>32.2762</v>
+        <v>32.2273</v>
       </c>
       <c r="E15" t="n">
-        <v>12.5701</v>
+        <v>12.5555</v>
       </c>
       <c r="F15" t="n">
-        <v>13.0398</v>
+        <v>12.9705</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>10.4931</v>
+        <v>10.4985</v>
       </c>
       <c r="C16" t="n">
-        <v>10.9329</v>
+        <v>10.8852</v>
       </c>
       <c r="D16" t="n">
-        <v>32.9122</v>
+        <v>32.7407</v>
       </c>
       <c r="E16" t="n">
-        <v>12.6882</v>
+        <v>12.6645</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1731</v>
+        <v>13.1667</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>10.7983</v>
+        <v>10.7967</v>
       </c>
       <c r="C17" t="n">
-        <v>11.3415</v>
+        <v>11.3069</v>
       </c>
       <c r="D17" t="n">
-        <v>33.4098</v>
+        <v>33.3785</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8518</v>
+        <v>12.8218</v>
       </c>
       <c r="F17" t="n">
-        <v>13.3179</v>
+        <v>13.2937</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>11.2877</v>
+        <v>11.2822</v>
       </c>
       <c r="C18" t="n">
-        <v>11.8824</v>
+        <v>11.9236</v>
       </c>
       <c r="D18" t="n">
-        <v>33.7213</v>
+        <v>34.2219</v>
       </c>
       <c r="E18" t="n">
-        <v>13.0426</v>
+        <v>13.0074</v>
       </c>
       <c r="F18" t="n">
-        <v>13.4841</v>
+        <v>13.4868</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>11.9358</v>
+        <v>11.9255</v>
       </c>
       <c r="C19" t="n">
-        <v>12.6849</v>
+        <v>12.6816</v>
       </c>
       <c r="D19" t="n">
-        <v>35.0423</v>
+        <v>34.5028</v>
       </c>
       <c r="E19" t="n">
-        <v>13.3107</v>
+        <v>13.2752</v>
       </c>
       <c r="F19" t="n">
-        <v>13.811</v>
+        <v>13.8104</v>
       </c>
     </row>
     <row r="20">
@@ -5442,16 +5442,16 @@
         <v>12.9574</v>
       </c>
       <c r="C20" t="n">
-        <v>13.8484</v>
+        <v>13.8847</v>
       </c>
       <c r="D20" t="n">
-        <v>35.8575</v>
+        <v>35.2912</v>
       </c>
       <c r="E20" t="n">
-        <v>13.9305</v>
+        <v>13.9154</v>
       </c>
       <c r="F20" t="n">
-        <v>14.4903</v>
+        <v>14.525</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>14.6908</v>
+        <v>14.6692</v>
       </c>
       <c r="C21" t="n">
-        <v>15.5886</v>
+        <v>15.5708</v>
       </c>
       <c r="D21" t="n">
-        <v>29.0826</v>
+        <v>28.6076</v>
       </c>
       <c r="E21" t="n">
-        <v>14.8863</v>
+        <v>14.8452</v>
       </c>
       <c r="F21" t="n">
-        <v>15.5682</v>
+        <v>15.5828</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>17.3001</v>
+        <v>17.2755</v>
       </c>
       <c r="C22" t="n">
-        <v>18.2678</v>
+        <v>18.2746</v>
       </c>
       <c r="D22" t="n">
-        <v>29.7227</v>
+        <v>29.8154</v>
       </c>
       <c r="E22" t="n">
-        <v>16.8804</v>
+        <v>16.8496</v>
       </c>
       <c r="F22" t="n">
-        <v>17.7076</v>
+        <v>17.6349</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>21.694</v>
+        <v>21.3129</v>
       </c>
       <c r="C23" t="n">
-        <v>22.4658</v>
+        <v>22.458</v>
       </c>
       <c r="D23" t="n">
-        <v>30.4573</v>
+        <v>30.4958</v>
       </c>
       <c r="E23" t="n">
-        <v>12.3541</v>
+        <v>12.3393</v>
       </c>
       <c r="F23" t="n">
-        <v>12.7967</v>
+        <v>12.7703</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>9.85507</v>
+        <v>9.8195</v>
       </c>
       <c r="C24" t="n">
-        <v>10.4014</v>
+        <v>10.393</v>
       </c>
       <c r="D24" t="n">
-        <v>31.1107</v>
+        <v>31.0529</v>
       </c>
       <c r="E24" t="n">
-        <v>12.4055</v>
+        <v>12.379</v>
       </c>
       <c r="F24" t="n">
-        <v>12.8216</v>
+        <v>12.8748</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>9.89476</v>
+        <v>9.87838</v>
       </c>
       <c r="C25" t="n">
-        <v>10.7241</v>
+        <v>10.5226</v>
       </c>
       <c r="D25" t="n">
-        <v>31.6571</v>
+        <v>31.7981</v>
       </c>
       <c r="E25" t="n">
-        <v>12.4456</v>
+        <v>12.4429</v>
       </c>
       <c r="F25" t="n">
-        <v>12.9363</v>
+        <v>12.9148</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>10.0524</v>
+        <v>10.0086</v>
       </c>
       <c r="C26" t="n">
-        <v>10.747</v>
+        <v>10.7306</v>
       </c>
       <c r="D26" t="n">
-        <v>32.0029</v>
+        <v>32.3321</v>
       </c>
       <c r="E26" t="n">
-        <v>12.4636</v>
+        <v>12.5222</v>
       </c>
       <c r="F26" t="n">
-        <v>13.0097</v>
+        <v>12.9973</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>10.0997</v>
+        <v>10.1215</v>
       </c>
       <c r="C27" t="n">
-        <v>10.8638</v>
+        <v>10.9283</v>
       </c>
       <c r="D27" t="n">
-        <v>33.0438</v>
+        <v>33.0461</v>
       </c>
       <c r="E27" t="n">
-        <v>12.5361</v>
+        <v>12.558</v>
       </c>
       <c r="F27" t="n">
-        <v>13.112</v>
+        <v>13.0958</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>10.2957</v>
+        <v>10.2722</v>
       </c>
       <c r="C28" t="n">
-        <v>11.0878</v>
+        <v>11.0745</v>
       </c>
       <c r="D28" t="n">
-        <v>33.769</v>
+        <v>33.6393</v>
       </c>
       <c r="E28" t="n">
-        <v>12.6431</v>
+        <v>12.6271</v>
       </c>
       <c r="F28" t="n">
-        <v>13.2077</v>
+        <v>13.2286</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>10.4699</v>
+        <v>10.4336</v>
       </c>
       <c r="C29" t="n">
-        <v>11.317</v>
+        <v>11.3289</v>
       </c>
       <c r="D29" t="n">
-        <v>34.0333</v>
+        <v>34.3396</v>
       </c>
       <c r="E29" t="n">
-        <v>12.7428</v>
+        <v>12.7331</v>
       </c>
       <c r="F29" t="n">
-        <v>13.3996</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>10.6694</v>
+        <v>10.6485</v>
       </c>
       <c r="C30" t="n">
-        <v>11.6072</v>
+        <v>11.5905</v>
       </c>
       <c r="D30" t="n">
-        <v>34.9675</v>
+        <v>34.7884</v>
       </c>
       <c r="E30" t="n">
-        <v>12.8872</v>
+        <v>12.8435</v>
       </c>
       <c r="F30" t="n">
-        <v>13.5221</v>
+        <v>13.5269</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>10.9613</v>
+        <v>10.9245</v>
       </c>
       <c r="C31" t="n">
-        <v>11.9156</v>
+        <v>11.905</v>
       </c>
       <c r="D31" t="n">
-        <v>36.3068</v>
+        <v>35.8001</v>
       </c>
       <c r="E31" t="n">
-        <v>13.0228</v>
+        <v>13.0012</v>
       </c>
       <c r="F31" t="n">
-        <v>13.7456</v>
+        <v>13.7687</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>11.3758</v>
+        <v>11.3297</v>
       </c>
       <c r="C32" t="n">
-        <v>12.388</v>
+        <v>12.3637</v>
       </c>
       <c r="D32" t="n">
-        <v>36.4821</v>
+        <v>36.5482</v>
       </c>
       <c r="E32" t="n">
-        <v>13.1921</v>
+        <v>13.1959</v>
       </c>
       <c r="F32" t="n">
-        <v>13.9503</v>
+        <v>13.9734</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>11.9318</v>
+        <v>11.9331</v>
       </c>
       <c r="C33" t="n">
-        <v>12.9156</v>
+        <v>12.9424</v>
       </c>
       <c r="D33" t="n">
-        <v>37.1592</v>
+        <v>37.1647</v>
       </c>
       <c r="E33" t="n">
-        <v>13.4701</v>
+        <v>13.4469</v>
       </c>
       <c r="F33" t="n">
-        <v>14.2338</v>
+        <v>14.2645</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>13.0511</v>
+        <v>13.0345</v>
       </c>
       <c r="C34" t="n">
-        <v>13.9694</v>
+        <v>14.0536</v>
       </c>
       <c r="D34" t="n">
-        <v>37.8684</v>
+        <v>37.9603</v>
       </c>
       <c r="E34" t="n">
-        <v>13.9746</v>
+        <v>13.9663</v>
       </c>
       <c r="F34" t="n">
-        <v>14.7719</v>
+        <v>14.7598</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>14.4722</v>
+        <v>14.502</v>
       </c>
       <c r="C35" t="n">
-        <v>15.5719</v>
+        <v>15.5772</v>
       </c>
       <c r="D35" t="n">
-        <v>29.9645</v>
+        <v>29.8396</v>
       </c>
       <c r="E35" t="n">
-        <v>14.8476</v>
+        <v>14.8386</v>
       </c>
       <c r="F35" t="n">
-        <v>15.7225</v>
+        <v>15.6482</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.0274</v>
+        <v>17.0213</v>
       </c>
       <c r="C36" t="n">
-        <v>18.2124</v>
+        <v>18.1818</v>
       </c>
       <c r="D36" t="n">
-        <v>31.3869</v>
+        <v>30.699</v>
       </c>
       <c r="E36" t="n">
-        <v>16.3206</v>
+        <v>16.303</v>
       </c>
       <c r="F36" t="n">
-        <v>17.1911</v>
+        <v>17.1845</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>20.4563</v>
+        <v>20.5122</v>
       </c>
       <c r="C37" t="n">
-        <v>21.5912</v>
+        <v>21.2959</v>
       </c>
       <c r="D37" t="n">
-        <v>31.3633</v>
+        <v>31.3655</v>
       </c>
       <c r="E37" t="n">
-        <v>12.5714</v>
+        <v>12.5698</v>
       </c>
       <c r="F37" t="n">
-        <v>13.128</v>
+        <v>13.1273</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>10.0102</v>
+        <v>10.0143</v>
       </c>
       <c r="C38" t="n">
-        <v>10.7854</v>
+        <v>10.7839</v>
       </c>
       <c r="D38" t="n">
-        <v>32.2189</v>
+        <v>32.2073</v>
       </c>
       <c r="E38" t="n">
-        <v>12.6357</v>
+        <v>12.5954</v>
       </c>
       <c r="F38" t="n">
-        <v>13.2286</v>
+        <v>13.2013</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>10.0858</v>
+        <v>10.0879</v>
       </c>
       <c r="C39" t="n">
-        <v>10.8788</v>
+        <v>10.9343</v>
       </c>
       <c r="D39" t="n">
-        <v>33.703</v>
+        <v>34.6535</v>
       </c>
       <c r="E39" t="n">
-        <v>12.5981</v>
+        <v>12.6886</v>
       </c>
       <c r="F39" t="n">
-        <v>13.3288</v>
+        <v>13.2747</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>10.154</v>
+        <v>10.1565</v>
       </c>
       <c r="C40" t="n">
-        <v>11.0136</v>
+        <v>11.3124</v>
       </c>
       <c r="D40" t="n">
-        <v>34.2249</v>
+        <v>33.6796</v>
       </c>
       <c r="E40" t="n">
-        <v>12.655</v>
+        <v>12.6844</v>
       </c>
       <c r="F40" t="n">
-        <v>13.3568</v>
+        <v>13.3206</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>10.2067</v>
+        <v>10.2481</v>
       </c>
       <c r="C41" t="n">
-        <v>11.1399</v>
+        <v>11.1461</v>
       </c>
       <c r="D41" t="n">
-        <v>34.4313</v>
+        <v>35.031</v>
       </c>
       <c r="E41" t="n">
-        <v>12.7848</v>
+        <v>12.7374</v>
       </c>
       <c r="F41" t="n">
-        <v>13.4188</v>
+        <v>13.4065</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>10.3975</v>
+        <v>10.384</v>
       </c>
       <c r="C42" t="n">
-        <v>11.3179</v>
+        <v>11.3632</v>
       </c>
       <c r="D42" t="n">
-        <v>35.6695</v>
+        <v>36.2709</v>
       </c>
       <c r="E42" t="n">
-        <v>12.8215</v>
+        <v>12.8223</v>
       </c>
       <c r="F42" t="n">
-        <v>13.5249</v>
+        <v>13.5232</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>10.5721</v>
+        <v>10.5786</v>
       </c>
       <c r="C43" t="n">
-        <v>11.5208</v>
+        <v>11.6508</v>
       </c>
       <c r="D43" t="n">
-        <v>36.5214</v>
+        <v>36.6967</v>
       </c>
       <c r="E43" t="n">
-        <v>12.8665</v>
+        <v>12.9018</v>
       </c>
       <c r="F43" t="n">
-        <v>13.5811</v>
+        <v>13.6133</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>10.7375</v>
+        <v>10.7173</v>
       </c>
       <c r="C44" t="n">
-        <v>11.7856</v>
+        <v>11.76</v>
       </c>
       <c r="D44" t="n">
-        <v>36.9939</v>
+        <v>37.712</v>
       </c>
       <c r="E44" t="n">
-        <v>13.0284</v>
+        <v>13.0283</v>
       </c>
       <c r="F44" t="n">
-        <v>13.7753</v>
+        <v>13.7725</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>11.0585</v>
+        <v>11.0097</v>
       </c>
       <c r="C45" t="n">
-        <v>12.1332</v>
+        <v>12.0272</v>
       </c>
       <c r="D45" t="n">
-        <v>37.6817</v>
+        <v>37.6837</v>
       </c>
       <c r="E45" t="n">
-        <v>13.196</v>
+        <v>13.1537</v>
       </c>
       <c r="F45" t="n">
-        <v>13.9882</v>
+        <v>13.9442</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>11.4958</v>
+        <v>11.5046</v>
       </c>
       <c r="C46" t="n">
-        <v>12.6683</v>
+        <v>12.6266</v>
       </c>
       <c r="D46" t="n">
-        <v>39.8625</v>
+        <v>40.4635</v>
       </c>
       <c r="E46" t="n">
-        <v>13.3644</v>
+        <v>13.3645</v>
       </c>
       <c r="F46" t="n">
-        <v>14.1672</v>
+        <v>14.1864</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>12.0777</v>
+        <v>12.0752</v>
       </c>
       <c r="C47" t="n">
-        <v>13.1718</v>
+        <v>13.264</v>
       </c>
       <c r="D47" t="n">
-        <v>42.339</v>
+        <v>40.8735</v>
       </c>
       <c r="E47" t="n">
-        <v>13.6266</v>
+        <v>13.7447</v>
       </c>
       <c r="F47" t="n">
-        <v>14.4771</v>
+        <v>14.4387</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>13.0083</v>
+        <v>12.9846</v>
       </c>
       <c r="C48" t="n">
-        <v>14.2092</v>
+        <v>14.1483</v>
       </c>
       <c r="D48" t="n">
-        <v>40.9924</v>
+        <v>43.2673</v>
       </c>
       <c r="E48" t="n">
-        <v>14.1054</v>
+        <v>14.1062</v>
       </c>
       <c r="F48" t="n">
-        <v>15.0049</v>
+        <v>14.9755</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.333</v>
+        <v>14.3124</v>
       </c>
       <c r="C49" t="n">
-        <v>15.6043</v>
+        <v>15.7197</v>
       </c>
       <c r="D49" t="n">
-        <v>44.6943</v>
+        <v>43.1425</v>
       </c>
       <c r="E49" t="n">
-        <v>14.814</v>
+        <v>14.8055</v>
       </c>
       <c r="F49" t="n">
-        <v>15.7779</v>
+        <v>15.7254</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>16.3971</v>
+        <v>16.3697</v>
       </c>
       <c r="C50" t="n">
-        <v>17.7301</v>
+        <v>17.7804</v>
       </c>
       <c r="D50" t="n">
-        <v>36.7188</v>
+        <v>36.5459</v>
       </c>
       <c r="E50" t="n">
-        <v>15.9782</v>
+        <v>15.9842</v>
       </c>
       <c r="F50" t="n">
-        <v>16.9742</v>
+        <v>16.9073</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>19.6993</v>
+        <v>19.738</v>
       </c>
       <c r="C51" t="n">
-        <v>21.0729</v>
+        <v>21.0131</v>
       </c>
       <c r="D51" t="n">
-        <v>38.0033</v>
+        <v>38.1924</v>
       </c>
       <c r="E51" t="n">
-        <v>13.067</v>
+        <v>12.8492</v>
       </c>
       <c r="F51" t="n">
-        <v>13.6679</v>
+        <v>13.7513</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>24.9981</v>
+        <v>24.8661</v>
       </c>
       <c r="C52" t="n">
-        <v>26.5397</v>
+        <v>26.5581</v>
       </c>
       <c r="D52" t="n">
-        <v>39.4875</v>
+        <v>39.142</v>
       </c>
       <c r="E52" t="n">
-        <v>13.5762</v>
+        <v>13.126</v>
       </c>
       <c r="F52" t="n">
-        <v>13.9832</v>
+        <v>13.9387</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>10.5704</v>
+        <v>10.6102</v>
       </c>
       <c r="C53" t="n">
-        <v>11.713</v>
+        <v>11.8278</v>
       </c>
       <c r="D53" t="n">
-        <v>40.5824</v>
+        <v>41.1631</v>
       </c>
       <c r="E53" t="n">
-        <v>13.2104</v>
+        <v>13.0998</v>
       </c>
       <c r="F53" t="n">
-        <v>14.214</v>
+        <v>13.9514</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>10.5084</v>
+        <v>10.4595</v>
       </c>
       <c r="C54" t="n">
-        <v>11.5394</v>
+        <v>12.0362</v>
       </c>
       <c r="D54" t="n">
-        <v>39.8402</v>
+        <v>47.4542</v>
       </c>
       <c r="E54" t="n">
-        <v>13.1167</v>
+        <v>13.1134</v>
       </c>
       <c r="F54" t="n">
-        <v>14.2114</v>
+        <v>14.0237</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>10.9322</v>
+        <v>10.9098</v>
       </c>
       <c r="C55" t="n">
-        <v>12.2655</v>
+        <v>12.5842</v>
       </c>
       <c r="D55" t="n">
-        <v>46.614</v>
+        <v>46.7166</v>
       </c>
       <c r="E55" t="n">
-        <v>13.2223</v>
+        <v>13.2588</v>
       </c>
       <c r="F55" t="n">
-        <v>14.3909</v>
+        <v>14.0882</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>10.8409</v>
+        <v>10.6377</v>
       </c>
       <c r="C56" t="n">
-        <v>11.8975</v>
+        <v>12.4055</v>
       </c>
       <c r="D56" t="n">
-        <v>47.5914</v>
+        <v>49.949</v>
       </c>
       <c r="E56" t="n">
-        <v>13.2664</v>
+        <v>13.3293</v>
       </c>
       <c r="F56" t="n">
-        <v>14.0626</v>
+        <v>14.1855</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>10.9364</v>
+        <v>10.6526</v>
       </c>
       <c r="C57" t="n">
-        <v>12.6446</v>
+        <v>12.7321</v>
       </c>
       <c r="D57" t="n">
-        <v>54.0589</v>
+        <v>54.8412</v>
       </c>
       <c r="E57" t="n">
-        <v>14.0848</v>
+        <v>13.9545</v>
       </c>
       <c r="F57" t="n">
-        <v>14.495</v>
+        <v>14.4072</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>11.2758</v>
+        <v>11.2838</v>
       </c>
       <c r="C58" t="n">
-        <v>12.3588</v>
+        <v>12.9268</v>
       </c>
       <c r="D58" t="n">
-        <v>51.6314</v>
+        <v>56.5455</v>
       </c>
       <c r="E58" t="n">
-        <v>13.6285</v>
+        <v>13.1633</v>
       </c>
       <c r="F58" t="n">
-        <v>14.478</v>
+        <v>14.1048</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>11.142</v>
+        <v>11.3187</v>
       </c>
       <c r="C59" t="n">
-        <v>13.4767</v>
+        <v>13.4248</v>
       </c>
       <c r="D59" t="n">
-        <v>63.3473</v>
+        <v>61.6359</v>
       </c>
       <c r="E59" t="n">
-        <v>13.6467</v>
+        <v>14.0433</v>
       </c>
       <c r="F59" t="n">
-        <v>14.5738</v>
+        <v>14.8957</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>11.7384</v>
+        <v>11.7751</v>
       </c>
       <c r="C60" t="n">
-        <v>13.113</v>
+        <v>13.5969</v>
       </c>
       <c r="D60" t="n">
-        <v>65.8789</v>
+        <v>64.2209</v>
       </c>
       <c r="E60" t="n">
-        <v>13.8791</v>
+        <v>13.8252</v>
       </c>
       <c r="F60" t="n">
-        <v>14.8454</v>
+        <v>15.1418</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>12.2522</v>
+        <v>12.2936</v>
       </c>
       <c r="C61" t="n">
-        <v>14.5561</v>
+        <v>14.3069</v>
       </c>
       <c r="D61" t="n">
-        <v>72.34529999999999</v>
+        <v>74.3595</v>
       </c>
       <c r="E61" t="n">
-        <v>13.8835</v>
+        <v>14.1445</v>
       </c>
       <c r="F61" t="n">
-        <v>15.4894</v>
+        <v>15.7162</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>13.2244</v>
+        <v>13.1511</v>
       </c>
       <c r="C62" t="n">
-        <v>14.7406</v>
+        <v>15.2212</v>
       </c>
       <c r="D62" t="n">
-        <v>77.854</v>
+        <v>78.83540000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>14.5383</v>
+        <v>14.2206</v>
       </c>
       <c r="F62" t="n">
-        <v>15.7783</v>
+        <v>15.8962</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.302</v>
+        <v>14.3229</v>
       </c>
       <c r="C63" t="n">
-        <v>16.545</v>
+        <v>16.7143</v>
       </c>
       <c r="D63" t="n">
-        <v>88.0543</v>
+        <v>86.9862</v>
       </c>
       <c r="E63" t="n">
-        <v>15.0463</v>
+        <v>15.2916</v>
       </c>
       <c r="F63" t="n">
-        <v>16.6716</v>
+        <v>17.1071</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>16.2237</v>
+        <v>16.1529</v>
       </c>
       <c r="C64" t="n">
-        <v>18.6308</v>
+        <v>18.7625</v>
       </c>
       <c r="D64" t="n">
-        <v>74.85939999999999</v>
+        <v>77.5127</v>
       </c>
       <c r="E64" t="n">
-        <v>16.3269</v>
+        <v>16.0309</v>
       </c>
       <c r="F64" t="n">
-        <v>17.7118</v>
+        <v>18.0268</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>18.977</v>
+        <v>19.0573</v>
       </c>
       <c r="C65" t="n">
-        <v>21.5262</v>
+        <v>21.4835</v>
       </c>
       <c r="D65" t="n">
-        <v>81.1904</v>
+        <v>83.6965</v>
       </c>
       <c r="E65" t="n">
-        <v>18.4112</v>
+        <v>18.616</v>
       </c>
       <c r="F65" t="n">
-        <v>19.2196</v>
+        <v>19.9023</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>23.997</v>
+        <v>24.2069</v>
       </c>
       <c r="C66" t="n">
-        <v>25.3933</v>
+        <v>25.6731</v>
       </c>
       <c r="D66" t="n">
-        <v>86.4332</v>
+        <v>88.6405</v>
       </c>
       <c r="E66" t="n">
-        <v>15.1568</v>
+        <v>14.9436</v>
       </c>
       <c r="F66" t="n">
-        <v>15.9097</v>
+        <v>15.9799</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>12.2464</v>
+        <v>12.2629</v>
       </c>
       <c r="C67" t="n">
-        <v>13.978</v>
+        <v>13.8475</v>
       </c>
       <c r="D67" t="n">
-        <v>94.1058</v>
+        <v>94.8579</v>
       </c>
       <c r="E67" t="n">
-        <v>14.9435</v>
+        <v>14.3737</v>
       </c>
       <c r="F67" t="n">
-        <v>16.026</v>
+        <v>15.9839</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>12.392</v>
+        <v>12.3551</v>
       </c>
       <c r="C68" t="n">
-        <v>14.1128</v>
+        <v>14.1894</v>
       </c>
       <c r="D68" t="n">
-        <v>99.6952</v>
+        <v>99.6695</v>
       </c>
       <c r="E68" t="n">
-        <v>15.0847</v>
+        <v>14.5443</v>
       </c>
       <c r="F68" t="n">
-        <v>15.9263</v>
+        <v>15.7664</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>12.2831</v>
+        <v>12.3001</v>
       </c>
       <c r="C69" t="n">
-        <v>14.3715</v>
+        <v>14.4974</v>
       </c>
       <c r="D69" t="n">
-        <v>105.334</v>
+        <v>106.304</v>
       </c>
       <c r="E69" t="n">
-        <v>15.0472</v>
+        <v>15.1773</v>
       </c>
       <c r="F69" t="n">
-        <v>15.5472</v>
+        <v>15.8954</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>12.467</v>
+        <v>12.452</v>
       </c>
       <c r="C70" t="n">
-        <v>14.595</v>
+        <v>14.5769</v>
       </c>
       <c r="D70" t="n">
-        <v>111.277</v>
+        <v>112.018</v>
       </c>
       <c r="E70" t="n">
-        <v>15.132</v>
+        <v>15.2454</v>
       </c>
       <c r="F70" t="n">
-        <v>16.2384</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>12.6188</v>
+        <v>12.5682</v>
       </c>
       <c r="C71" t="n">
-        <v>14.8176</v>
+        <v>14.775</v>
       </c>
       <c r="D71" t="n">
-        <v>118.77</v>
+        <v>118.71</v>
       </c>
       <c r="E71" t="n">
-        <v>15.2478</v>
+        <v>15.3345</v>
       </c>
       <c r="F71" t="n">
-        <v>16.2032</v>
+        <v>16.4632</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>12.8093</v>
+        <v>12.2849</v>
       </c>
       <c r="C72" t="n">
-        <v>15.2019</v>
+        <v>15.4262</v>
       </c>
       <c r="D72" t="n">
-        <v>126.951</v>
+        <v>126.714</v>
       </c>
       <c r="E72" t="n">
-        <v>15.4203</v>
+        <v>15.5282</v>
       </c>
       <c r="F72" t="n">
-        <v>16.6298</v>
+        <v>16.7666</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>13.0727</v>
+        <v>13.0395</v>
       </c>
       <c r="C73" t="n">
-        <v>15.1589</v>
+        <v>14.8767</v>
       </c>
       <c r="D73" t="n">
-        <v>137.583</v>
+        <v>138.178</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5579</v>
+        <v>15.6181</v>
       </c>
       <c r="F73" t="n">
-        <v>16.1261</v>
+        <v>17.0218</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>13.5411</v>
+        <v>13.4286</v>
       </c>
       <c r="C74" t="n">
-        <v>15.4628</v>
+        <v>16.0378</v>
       </c>
       <c r="D74" t="n">
-        <v>148.63</v>
+        <v>149.161</v>
       </c>
       <c r="E74" t="n">
-        <v>15.7737</v>
+        <v>15.7796</v>
       </c>
       <c r="F74" t="n">
-        <v>16.942</v>
+        <v>17.2216</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.0643</v>
+        <v>14.0518</v>
       </c>
       <c r="C75" t="n">
-        <v>16.3138</v>
+        <v>17.0327</v>
       </c>
       <c r="D75" t="n">
-        <v>162.518</v>
+        <v>161.067</v>
       </c>
       <c r="E75" t="n">
-        <v>16.203</v>
+        <v>16.071</v>
       </c>
       <c r="F75" t="n">
-        <v>17.3638</v>
+        <v>17.3506</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.8935</v>
+        <v>14.7999</v>
       </c>
       <c r="C76" t="n">
-        <v>18.6797</v>
+        <v>18.5509</v>
       </c>
       <c r="D76" t="n">
-        <v>150.504</v>
+        <v>151.699</v>
       </c>
       <c r="E76" t="n">
-        <v>16.3391</v>
+        <v>16.2635</v>
       </c>
       <c r="F76" t="n">
-        <v>17.9681</v>
+        <v>18.0236</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>15.8512</v>
+        <v>15.8534</v>
       </c>
       <c r="C77" t="n">
-        <v>20.4127</v>
+        <v>21.0264</v>
       </c>
       <c r="D77" t="n">
-        <v>158.474</v>
+        <v>157.9</v>
       </c>
       <c r="E77" t="n">
-        <v>16.9481</v>
+        <v>16.9398</v>
       </c>
       <c r="F77" t="n">
-        <v>18.6948</v>
+        <v>18.7764</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.6678</v>
+        <v>17.4533</v>
       </c>
       <c r="C78" t="n">
-        <v>23.5582</v>
+        <v>24.0772</v>
       </c>
       <c r="D78" t="n">
-        <v>127.809</v>
+        <v>128.606</v>
       </c>
       <c r="E78" t="n">
-        <v>17.8945</v>
+        <v>17.9035</v>
       </c>
       <c r="F78" t="n">
-        <v>19.8914</v>
+        <v>20.1179</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>20.0059</v>
+        <v>20.113</v>
       </c>
       <c r="C79" t="n">
-        <v>28.2921</v>
+        <v>28.2003</v>
       </c>
       <c r="D79" t="n">
-        <v>134.225</v>
+        <v>134.925</v>
       </c>
       <c r="E79" t="n">
-        <v>19.7559</v>
+        <v>19.6716</v>
       </c>
       <c r="F79" t="n">
-        <v>21.9339</v>
+        <v>22.2446</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>23.9581</v>
+        <v>24.4778</v>
       </c>
       <c r="C80" t="n">
-        <v>34.344</v>
+        <v>35.3076</v>
       </c>
       <c r="D80" t="n">
-        <v>149.173</v>
+        <v>148.114</v>
       </c>
       <c r="E80" t="n">
-        <v>16.6282</v>
+        <v>16.6087</v>
       </c>
       <c r="F80" t="n">
-        <v>16.8256</v>
+        <v>17.3465</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>12.8581</v>
+        <v>13.7583</v>
       </c>
       <c r="C81" t="n">
-        <v>16.2232</v>
+        <v>16.4216</v>
       </c>
       <c r="D81" t="n">
-        <v>143.15</v>
+        <v>143.744</v>
       </c>
       <c r="E81" t="n">
-        <v>16.694</v>
+        <v>16.6964</v>
       </c>
       <c r="F81" t="n">
-        <v>17.5467</v>
+        <v>17.5382</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.6569</v>
+        <v>13.8548</v>
       </c>
       <c r="C82" t="n">
-        <v>17.1738</v>
+        <v>17.2562</v>
       </c>
       <c r="D82" t="n">
-        <v>159.001</v>
+        <v>158.413</v>
       </c>
       <c r="E82" t="n">
-        <v>16.788</v>
+        <v>16.8811</v>
       </c>
       <c r="F82" t="n">
-        <v>17.5722</v>
+        <v>17.7682</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.0401</v>
+        <v>13.961</v>
       </c>
       <c r="C83" t="n">
-        <v>17.7858</v>
+        <v>18.1894</v>
       </c>
       <c r="D83" t="n">
-        <v>152.82</v>
+        <v>153.711</v>
       </c>
       <c r="E83" t="n">
-        <v>16.8358</v>
+        <v>16.8196</v>
       </c>
       <c r="F83" t="n">
-        <v>17.91</v>
+        <v>17.946</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>14.1676</v>
+        <v>14.1389</v>
       </c>
       <c r="C84" t="n">
-        <v>18.6814</v>
+        <v>18.6759</v>
       </c>
       <c r="D84" t="n">
-        <v>161.899</v>
+        <v>161.732</v>
       </c>
       <c r="E84" t="n">
-        <v>16.9025</v>
+        <v>16.8747</v>
       </c>
       <c r="F84" t="n">
-        <v>17.9827</v>
+        <v>17.9288</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.2928</v>
+        <v>13.2573</v>
       </c>
       <c r="C85" t="n">
-        <v>20.0065</v>
+        <v>20.4296</v>
       </c>
       <c r="D85" t="n">
-        <v>163.314</v>
+        <v>163.794</v>
       </c>
       <c r="E85" t="n">
-        <v>16.9923</v>
+        <v>16.2804</v>
       </c>
       <c r="F85" t="n">
-        <v>18.3903</v>
+        <v>18.563</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>13.6475</v>
+        <v>13.5127</v>
       </c>
       <c r="C86" t="n">
-        <v>20.9329</v>
+        <v>21.7992</v>
       </c>
       <c r="D86" t="n">
-        <v>168.26</v>
+        <v>169.266</v>
       </c>
       <c r="E86" t="n">
-        <v>17.1585</v>
+        <v>17.1717</v>
       </c>
       <c r="F86" t="n">
-        <v>18.9894</v>
+        <v>18.9154</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>14.9392</v>
+        <v>14.8269</v>
       </c>
       <c r="C87" t="n">
-        <v>22.8903</v>
+        <v>22.9343</v>
       </c>
       <c r="D87" t="n">
-        <v>197.702</v>
+        <v>197.387</v>
       </c>
       <c r="E87" t="n">
-        <v>17.399</v>
+        <v>17.4005</v>
       </c>
       <c r="F87" t="n">
-        <v>19.3884</v>
+        <v>19.5856</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.2879</v>
+        <v>15.398</v>
       </c>
       <c r="C88" t="n">
-        <v>25.1767</v>
+        <v>25.0458</v>
       </c>
       <c r="D88" t="n">
-        <v>180.087</v>
+        <v>180.79</v>
       </c>
       <c r="E88" t="n">
-        <v>17.7192</v>
+        <v>17.6235</v>
       </c>
       <c r="F88" t="n">
-        <v>20.0868</v>
+        <v>20.1342</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>16.028</v>
+        <v>16.2034</v>
       </c>
       <c r="C89" t="n">
-        <v>26.5406</v>
+        <v>26.636</v>
       </c>
       <c r="D89" t="n">
-        <v>194.148</v>
+        <v>194.448</v>
       </c>
       <c r="E89" t="n">
-        <v>17.8662</v>
+        <v>17.9009</v>
       </c>
       <c r="F89" t="n">
-        <v>21.3411</v>
+        <v>21.4049</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.1675</v>
+        <v>17.2671</v>
       </c>
       <c r="C90" t="n">
-        <v>29.2621</v>
+        <v>29.1255</v>
       </c>
       <c r="D90" t="n">
-        <v>191.319</v>
+        <v>193.628</v>
       </c>
       <c r="E90" t="n">
-        <v>18.4776</v>
+        <v>18.4395</v>
       </c>
       <c r="F90" t="n">
-        <v>22.4486</v>
+        <v>22.7379</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.566</v>
+        <v>17.4992</v>
       </c>
       <c r="C91" t="n">
-        <v>31.2116</v>
+        <v>31.0698</v>
       </c>
       <c r="D91" t="n">
-        <v>201.15</v>
+        <v>201.903</v>
       </c>
       <c r="E91" t="n">
-        <v>19.2803</v>
+        <v>19.2312</v>
       </c>
       <c r="F91" t="n">
-        <v>24.3606</v>
+        <v>24.3292</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>20.268</v>
+        <v>20.3481</v>
       </c>
       <c r="C92" t="n">
-        <v>35.2803</v>
+        <v>35.3497</v>
       </c>
       <c r="D92" t="n">
-        <v>157.923</v>
+        <v>158.311</v>
       </c>
       <c r="E92" t="n">
-        <v>20.3799</v>
+        <v>20.3863</v>
       </c>
       <c r="F92" t="n">
-        <v>26.0682</v>
+        <v>26.4698</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>23.8106</v>
+        <v>23.7642</v>
       </c>
       <c r="C93" t="n">
-        <v>39.8468</v>
+        <v>39.7825</v>
       </c>
       <c r="D93" t="n">
-        <v>161.97</v>
+        <v>162.207</v>
       </c>
       <c r="E93" t="n">
-        <v>21.5553</v>
+        <v>22.3647</v>
       </c>
       <c r="F93" t="n">
-        <v>29.2311</v>
+        <v>29.6021</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>28.6583</v>
+        <v>28.5882</v>
       </c>
       <c r="C94" t="n">
-        <v>47.4375</v>
+        <v>47.6646</v>
       </c>
       <c r="D94" t="n">
-        <v>166.058</v>
+        <v>166.916</v>
       </c>
       <c r="E94" t="n">
-        <v>17.3179</v>
+        <v>17.7259</v>
       </c>
       <c r="F94" t="n">
-        <v>20.4845</v>
+        <v>20.2621</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>15.5146</v>
+        <v>15.5887</v>
       </c>
       <c r="C95" t="n">
-        <v>23.6306</v>
+        <v>24.347</v>
       </c>
       <c r="D95" t="n">
-        <v>170.525</v>
+        <v>171.289</v>
       </c>
       <c r="E95" t="n">
-        <v>17.8521</v>
+        <v>17.8623</v>
       </c>
       <c r="F95" t="n">
-        <v>21.0343</v>
+        <v>20.9096</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>16.0746</v>
+        <v>16.1618</v>
       </c>
       <c r="C96" t="n">
-        <v>24.8459</v>
+        <v>25.194</v>
       </c>
       <c r="D96" t="n">
-        <v>172.285</v>
+        <v>173.043</v>
       </c>
       <c r="E96" t="n">
-        <v>17.7368</v>
+        <v>17.7744</v>
       </c>
       <c r="F96" t="n">
-        <v>21.1927</v>
+        <v>21.5618</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>15.9783</v>
+        <v>16.1475</v>
       </c>
       <c r="C97" t="n">
-        <v>27.2699</v>
+        <v>26.7761</v>
       </c>
       <c r="D97" t="n">
-        <v>179.184</v>
+        <v>179.836</v>
       </c>
       <c r="E97" t="n">
-        <v>18.2801</v>
+        <v>18.2366</v>
       </c>
       <c r="F97" t="n">
-        <v>21.8752</v>
+        <v>22.3982</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>17.2638</v>
+        <v>17.2332</v>
       </c>
       <c r="C98" t="n">
-        <v>26.6638</v>
+        <v>27.3278</v>
       </c>
       <c r="D98" t="n">
-        <v>183.763</v>
+        <v>184.713</v>
       </c>
       <c r="E98" t="n">
-        <v>18.5814</v>
+        <v>18.3209</v>
       </c>
       <c r="F98" t="n">
-        <v>23.5205</v>
+        <v>23.138</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>17.9749</v>
+        <v>18.0116</v>
       </c>
       <c r="C99" t="n">
-        <v>27.9386</v>
+        <v>28.2663</v>
       </c>
       <c r="D99" t="n">
-        <v>188.991</v>
+        <v>190.278</v>
       </c>
       <c r="E99" t="n">
-        <v>19.0996</v>
+        <v>18.9777</v>
       </c>
       <c r="F99" t="n">
-        <v>23.7602</v>
+        <v>23.6994</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>18.349</v>
+        <v>18.7764</v>
       </c>
       <c r="C100" t="n">
-        <v>28.416</v>
+        <v>29.1945</v>
       </c>
       <c r="D100" t="n">
-        <v>194.831</v>
+        <v>195.585</v>
       </c>
       <c r="E100" t="n">
-        <v>19.1795</v>
+        <v>19.3666</v>
       </c>
       <c r="F100" t="n">
-        <v>25.3765</v>
+        <v>24.1733</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>18.9913</v>
+        <v>19.7423</v>
       </c>
       <c r="C101" t="n">
-        <v>30.1648</v>
+        <v>30.3565</v>
       </c>
       <c r="D101" t="n">
-        <v>199.702</v>
+        <v>201.372</v>
       </c>
       <c r="E101" t="n">
-        <v>19.6221</v>
+        <v>19.924</v>
       </c>
       <c r="F101" t="n">
-        <v>25.3765</v>
+        <v>25.4585</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3886</v>
+        <v>20.5629</v>
       </c>
       <c r="C102" t="n">
-        <v>32.6093</v>
+        <v>32.6906</v>
       </c>
       <c r="D102" t="n">
-        <v>211.426</v>
+        <v>211.867</v>
       </c>
       <c r="E102" t="n">
-        <v>20.1037</v>
+        <v>20.4171</v>
       </c>
       <c r="F102" t="n">
-        <v>26.3052</v>
+        <v>26.6567</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.7172</v>
+        <v>21.7493</v>
       </c>
       <c r="C103" t="n">
-        <v>33.295</v>
+        <v>33.3841</v>
       </c>
       <c r="D103" t="n">
-        <v>212.11</v>
+        <v>213.062</v>
       </c>
       <c r="E103" t="n">
-        <v>21.0943</v>
+        <v>20.7072</v>
       </c>
       <c r="F103" t="n">
-        <v>27.0425</v>
+        <v>27.0759</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.964</v>
+        <v>23.1148</v>
       </c>
       <c r="C104" t="n">
-        <v>34.917</v>
+        <v>35.0822</v>
       </c>
       <c r="D104" t="n">
-        <v>245.237</v>
+        <v>245.889</v>
       </c>
       <c r="E104" t="n">
-        <v>21.8324</v>
+        <v>21.8236</v>
       </c>
       <c r="F104" t="n">
-        <v>28.0169</v>
+        <v>27.6474</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>24.6071</v>
+        <v>24.7358</v>
       </c>
       <c r="C105" t="n">
-        <v>37.0279</v>
+        <v>37.7066</v>
       </c>
       <c r="D105" t="n">
-        <v>250.316</v>
+        <v>251.522</v>
       </c>
       <c r="E105" t="n">
-        <v>22.8355</v>
+        <v>22.8083</v>
       </c>
       <c r="F105" t="n">
-        <v>29.3906</v>
+        <v>29.3524</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>26.6996</v>
+        <v>26.4311</v>
       </c>
       <c r="C106" t="n">
-        <v>40.0413</v>
+        <v>42.7368</v>
       </c>
       <c r="D106" t="n">
-        <v>256.684</v>
+        <v>260.479</v>
       </c>
       <c r="E106" t="n">
-        <v>24.0499</v>
+        <v>23.3094</v>
       </c>
       <c r="F106" t="n">
-        <v>31.0648</v>
+        <v>31.0697</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>29.3645</v>
+        <v>29.8632</v>
       </c>
       <c r="C107" t="n">
-        <v>47.0051</v>
+        <v>45.0482</v>
       </c>
       <c r="D107" t="n">
-        <v>175.809</v>
+        <v>177.136</v>
       </c>
       <c r="E107" t="n">
-        <v>24.8574</v>
+        <v>24.873</v>
       </c>
       <c r="F107" t="n">
-        <v>33.9269</v>
+        <v>34.4564</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>34.8562</v>
+        <v>34.8965</v>
       </c>
       <c r="C108" t="n">
-        <v>55.3428</v>
+        <v>55.4735</v>
       </c>
       <c r="D108" t="n">
-        <v>180.42</v>
+        <v>181.287</v>
       </c>
       <c r="E108" t="n">
-        <v>19.9086</v>
+        <v>20.2015</v>
       </c>
       <c r="F108" t="n">
-        <v>24.3653</v>
+        <v>23.6119</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>42.4727</v>
+        <v>42.5448</v>
       </c>
       <c r="C109" t="n">
-        <v>65.9847</v>
+        <v>65.1352</v>
       </c>
       <c r="D109" t="n">
-        <v>184.801</v>
+        <v>185.646</v>
       </c>
       <c r="E109" t="n">
-        <v>20.6323</v>
+        <v>20.5908</v>
       </c>
       <c r="F109" t="n">
-        <v>24.7676</v>
+        <v>24.7098</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>19.7132</v>
+        <v>20.3839</v>
       </c>
       <c r="C110" t="n">
-        <v>29.5848</v>
+        <v>29.6921</v>
       </c>
       <c r="D110" t="n">
-        <v>188.213</v>
+        <v>189.687</v>
       </c>
       <c r="E110" t="n">
-        <v>20.8863</v>
+        <v>20.6805</v>
       </c>
       <c r="F110" t="n">
-        <v>25.2204</v>
+        <v>25.1843</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>20.7443</v>
+        <v>20.9237</v>
       </c>
       <c r="C111" t="n">
-        <v>30.4337</v>
+        <v>30.6372</v>
       </c>
       <c r="D111" t="n">
-        <v>193.33</v>
+        <v>194.152</v>
       </c>
       <c r="E111" t="n">
-        <v>20.6752</v>
+        <v>20.9949</v>
       </c>
       <c r="F111" t="n">
-        <v>25.6623</v>
+        <v>24.9112</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>20.6479</v>
+        <v>20.6364</v>
       </c>
       <c r="C112" t="n">
-        <v>31.2176</v>
+        <v>31.3126</v>
       </c>
       <c r="D112" t="n">
-        <v>198.487</v>
+        <v>199.234</v>
       </c>
       <c r="E112" t="n">
-        <v>21.3369</v>
+        <v>20.9163</v>
       </c>
       <c r="F112" t="n">
-        <v>26.0272</v>
+        <v>26.0585</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.7891</v>
+        <v>21.6987</v>
       </c>
       <c r="C113" t="n">
-        <v>32.2438</v>
+        <v>32.1817</v>
       </c>
       <c r="D113" t="n">
-        <v>203.136</v>
+        <v>204.191</v>
       </c>
       <c r="E113" t="n">
-        <v>21.6201</v>
+        <v>21.6074</v>
       </c>
       <c r="F113" t="n">
-        <v>26.5121</v>
+        <v>26.6099</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>22.3409</v>
+        <v>21.6273</v>
       </c>
       <c r="C114" t="n">
-        <v>33.0654</v>
+        <v>32.8105</v>
       </c>
       <c r="D114" t="n">
-        <v>208.246</v>
+        <v>209.439</v>
       </c>
       <c r="E114" t="n">
-        <v>21.9143</v>
+        <v>21.9476</v>
       </c>
       <c r="F114" t="n">
-        <v>26.3317</v>
+        <v>27.1229</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>22.9596</v>
+        <v>22.2465</v>
       </c>
       <c r="C115" t="n">
-        <v>34.3151</v>
+        <v>34.4627</v>
       </c>
       <c r="D115" t="n">
-        <v>214.156</v>
+        <v>214.812</v>
       </c>
       <c r="E115" t="n">
-        <v>22.2277</v>
+        <v>22.2803</v>
       </c>
       <c r="F115" t="n">
-        <v>26.8969</v>
+        <v>27.7419</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.5821</v>
+        <v>23.3062</v>
       </c>
       <c r="C116" t="n">
-        <v>35.6179</v>
+        <v>35.6668</v>
       </c>
       <c r="D116" t="n">
-        <v>219.48</v>
+        <v>220.714</v>
       </c>
       <c r="E116" t="n">
-        <v>22.6872</v>
+        <v>22.6437</v>
       </c>
       <c r="F116" t="n">
-        <v>27.5699</v>
+        <v>28.2137</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>24.6148</v>
+        <v>24.6684</v>
       </c>
       <c r="C117" t="n">
-        <v>37.2121</v>
+        <v>37.4812</v>
       </c>
       <c r="D117" t="n">
-        <v>226.803</v>
+        <v>227.693</v>
       </c>
       <c r="E117" t="n">
-        <v>23.1488</v>
+        <v>22.587</v>
       </c>
       <c r="F117" t="n">
-        <v>30.2782</v>
+        <v>29.9588</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.7921</v>
+        <v>25.8646</v>
       </c>
       <c r="C118" t="n">
-        <v>37.9742</v>
+        <v>38.4125</v>
       </c>
       <c r="D118" t="n">
-        <v>248.497</v>
+        <v>250.033</v>
       </c>
       <c r="E118" t="n">
-        <v>23.7444</v>
+        <v>23.8143</v>
       </c>
       <c r="F118" t="n">
-        <v>30.1969</v>
+        <v>30.4291</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>27.3556</v>
+        <v>28.1415</v>
       </c>
       <c r="C119" t="n">
-        <v>40.4376</v>
+        <v>42.337</v>
       </c>
       <c r="D119" t="n">
-        <v>239.892</v>
+        <v>240.457</v>
       </c>
       <c r="E119" t="n">
-        <v>24.5507</v>
+        <v>24.6001</v>
       </c>
       <c r="F119" t="n">
-        <v>31.3764</v>
+        <v>31.4944</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>29.603</v>
+        <v>29.653</v>
       </c>
       <c r="C120" t="n">
-        <v>45.3785</v>
+        <v>44.1288</v>
       </c>
       <c r="D120" t="n">
-        <v>268.566</v>
+        <v>270.734</v>
       </c>
       <c r="E120" t="n">
-        <v>25.7122</v>
+        <v>25.1703</v>
       </c>
       <c r="F120" t="n">
-        <v>32.4018</v>
+        <v>34.0927</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>32.7901</v>
+        <v>33.1729</v>
       </c>
       <c r="C121" t="n">
-        <v>49.6014</v>
+        <v>50.3842</v>
       </c>
       <c r="D121" t="n">
-        <v>183.526</v>
+        <v>190.178</v>
       </c>
       <c r="E121" t="n">
-        <v>27.4446</v>
+        <v>27.2338</v>
       </c>
       <c r="F121" t="n">
-        <v>36.2265</v>
+        <v>36.4443</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>37.4899</v>
+        <v>38.116</v>
       </c>
       <c r="C122" t="n">
-        <v>58.4093</v>
+        <v>58.9938</v>
       </c>
       <c r="D122" t="n">
-        <v>189.053</v>
+        <v>197.067</v>
       </c>
       <c r="E122" t="n">
-        <v>29.5861</v>
+        <v>30.7853</v>
       </c>
       <c r="F122" t="n">
-        <v>40.7575</v>
+        <v>40.5018</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>44.8217</v>
+        <v>46.1211</v>
       </c>
       <c r="C123" t="n">
-        <v>70.7375</v>
+        <v>72.35420000000001</v>
       </c>
       <c r="D123" t="n">
-        <v>193.599</v>
+        <v>201.606</v>
       </c>
       <c r="E123" t="n">
-        <v>21.159</v>
+        <v>22.9036</v>
       </c>
       <c r="F123" t="n">
-        <v>30.3647</v>
+        <v>28.1612</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>22.3859</v>
+        <v>22.9899</v>
       </c>
       <c r="C124" t="n">
-        <v>33.7597</v>
+        <v>32.5876</v>
       </c>
       <c r="D124" t="n">
-        <v>196.798</v>
+        <v>205.339</v>
       </c>
       <c r="E124" t="n">
-        <v>22.7179</v>
+        <v>22.4867</v>
       </c>
       <c r="F124" t="n">
-        <v>27.3689</v>
+        <v>31.1015</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2244</v>
+        <v>23.8135</v>
       </c>
       <c r="C125" t="n">
-        <v>34.3622</v>
+        <v>33.8492</v>
       </c>
       <c r="D125" t="n">
-        <v>201.465</v>
+        <v>210.705</v>
       </c>
       <c r="E125" t="n">
-        <v>24.0125</v>
+        <v>22.7532</v>
       </c>
       <c r="F125" t="n">
-        <v>28.9202</v>
+        <v>29.7861</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>23.2732</v>
+        <v>24.1845</v>
       </c>
       <c r="C126" t="n">
-        <v>36.9832</v>
+        <v>37.5068</v>
       </c>
       <c r="D126" t="n">
-        <v>206.11</v>
+        <v>215.516</v>
       </c>
       <c r="E126" t="n">
-        <v>22.8437</v>
+        <v>23.1152</v>
       </c>
       <c r="F126" t="n">
-        <v>29.5044</v>
+        <v>29.8566</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>23.6603</v>
+        <v>24.2947</v>
       </c>
       <c r="C127" t="n">
-        <v>38.3339</v>
+        <v>38.1372</v>
       </c>
       <c r="D127" t="n">
-        <v>211.964</v>
+        <v>220.761</v>
       </c>
       <c r="E127" t="n">
-        <v>23.8651</v>
+        <v>26.3166</v>
       </c>
       <c r="F127" t="n">
-        <v>28.8645</v>
+        <v>30.7642</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>23.9231</v>
+        <v>24.7515</v>
       </c>
       <c r="C128" t="n">
-        <v>38.4797</v>
+        <v>42.1884</v>
       </c>
       <c r="D128" t="n">
-        <v>216.369</v>
+        <v>226.659</v>
       </c>
       <c r="E128" t="n">
-        <v>23.3857</v>
+        <v>24.04</v>
       </c>
       <c r="F128" t="n">
-        <v>30.9617</v>
+        <v>31.7424</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>24.3667</v>
+        <v>26.4261</v>
       </c>
       <c r="C129" t="n">
-        <v>40.8902</v>
+        <v>41.2352</v>
       </c>
       <c r="D129" t="n">
-        <v>233.286</v>
+        <v>239.582</v>
       </c>
       <c r="E129" t="n">
-        <v>22.5273</v>
+        <v>22.9506</v>
       </c>
       <c r="F129" t="n">
-        <v>31.0075</v>
+        <v>32.0232</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>26.452</v>
+        <v>27.8342</v>
       </c>
       <c r="C130" t="n">
-        <v>41.6499</v>
+        <v>41.7223</v>
       </c>
       <c r="D130" t="n">
-        <v>238.049</v>
+        <v>244.783</v>
       </c>
       <c r="E130" t="n">
-        <v>23.8375</v>
+        <v>24.4213</v>
       </c>
       <c r="F130" t="n">
-        <v>31.8938</v>
+        <v>32.7862</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>26.8456</v>
+        <v>25.9896</v>
       </c>
       <c r="C131" t="n">
-        <v>47.8053</v>
+        <v>46.3749</v>
       </c>
       <c r="D131" t="n">
-        <v>250.543</v>
+        <v>251.62</v>
       </c>
       <c r="E131" t="n">
-        <v>23.4655</v>
+        <v>24.8691</v>
       </c>
       <c r="F131" t="n">
-        <v>33.562</v>
+        <v>33.703</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.5105</v>
+        <v>29.9212</v>
       </c>
       <c r="C132" t="n">
-        <v>48.6433</v>
+        <v>48.4868</v>
       </c>
       <c r="D132" t="n">
-        <v>256.285</v>
+        <v>257.947</v>
       </c>
       <c r="E132" t="n">
-        <v>25.5864</v>
+        <v>24.118</v>
       </c>
       <c r="F132" t="n">
-        <v>34.8647</v>
+        <v>34.5623</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>30.0519</v>
+        <v>30.222</v>
       </c>
       <c r="C133" t="n">
-        <v>50.5884</v>
+        <v>50.288</v>
       </c>
       <c r="D133" t="n">
-        <v>262.644</v>
+        <v>264.299</v>
       </c>
       <c r="E133" t="n">
-        <v>26.2887</v>
+        <v>26.6407</v>
       </c>
       <c r="F133" t="n">
-        <v>37.4474</v>
+        <v>37.7076</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>37.8094</v>
+        <v>33.0056</v>
       </c>
       <c r="C134" t="n">
-        <v>54.0373</v>
+        <v>55.5079</v>
       </c>
       <c r="D134" t="n">
-        <v>263.215</v>
+        <v>271.187</v>
       </c>
       <c r="E134" t="n">
-        <v>27.4113</v>
+        <v>30.6605</v>
       </c>
       <c r="F134" t="n">
-        <v>38.9312</v>
+        <v>39.1135</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>34.7333</v>
+        <v>36.0905</v>
       </c>
       <c r="C135" t="n">
-        <v>59.3878</v>
+        <v>60.6984</v>
       </c>
       <c r="D135" t="n">
-        <v>188.727</v>
+        <v>196.967</v>
       </c>
       <c r="E135" t="n">
-        <v>28.1131</v>
+        <v>29.482</v>
       </c>
       <c r="F135" t="n">
-        <v>40.4233</v>
+        <v>41.827</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>39.1433</v>
+        <v>38.9665</v>
       </c>
       <c r="C136" t="n">
-        <v>64.5278</v>
+        <v>74.0308</v>
       </c>
       <c r="D136" t="n">
-        <v>193.186</v>
+        <v>200.647</v>
       </c>
       <c r="E136" t="n">
-        <v>31.7123</v>
+        <v>31.8871</v>
       </c>
       <c r="F136" t="n">
-        <v>40.5744</v>
+        <v>43.4287</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>46.7386</v>
+        <v>47.158</v>
       </c>
       <c r="C137" t="n">
-        <v>80.3263</v>
+        <v>81.4492</v>
       </c>
       <c r="D137" t="n">
-        <v>200.67</v>
+        <v>208.051</v>
       </c>
       <c r="E137" t="n">
-        <v>41.2508</v>
+        <v>38.9216</v>
       </c>
       <c r="F137" t="n">
-        <v>51.1596</v>
+        <v>49.1656</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>47.1996</v>
+        <v>45.7382</v>
       </c>
       <c r="C138" t="n">
-        <v>60.0908</v>
+        <v>61.8342</v>
       </c>
       <c r="D138" t="n">
-        <v>203.974</v>
+        <v>212.679</v>
       </c>
       <c r="E138" t="n">
-        <v>41.7163</v>
+        <v>41.2606</v>
       </c>
       <c r="F138" t="n">
-        <v>51.3046</v>
+        <v>52.7202</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>44.7297</v>
+        <v>44.8421</v>
       </c>
       <c r="C139" t="n">
-        <v>60.6764</v>
+        <v>63.3904</v>
       </c>
       <c r="D139" t="n">
-        <v>208.304</v>
+        <v>217.329</v>
       </c>
       <c r="E139" t="n">
-        <v>43.0861</v>
+        <v>43.4941</v>
       </c>
       <c r="F139" t="n">
-        <v>52.6418</v>
+        <v>51.3561</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>44.3962</v>
+        <v>46.7235</v>
       </c>
       <c r="C140" t="n">
-        <v>61.894</v>
+        <v>61.5719</v>
       </c>
       <c r="D140" t="n">
-        <v>212.958</v>
+        <v>222.289</v>
       </c>
       <c r="E140" t="n">
-        <v>42.0883</v>
+        <v>43.5282</v>
       </c>
       <c r="F140" t="n">
-        <v>55.3245</v>
+        <v>54.2563</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>45.9353</v>
+        <v>48.5134</v>
       </c>
       <c r="C141" t="n">
-        <v>62.7536</v>
+        <v>65.0557</v>
       </c>
       <c r="D141" t="n">
-        <v>218.099</v>
+        <v>227.716</v>
       </c>
       <c r="E141" t="n">
-        <v>41.4683</v>
+        <v>44.42</v>
       </c>
       <c r="F141" t="n">
-        <v>55.6804</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>46.8927</v>
+        <v>48.2417</v>
       </c>
       <c r="C142" t="n">
-        <v>61.5344</v>
+        <v>66.8109</v>
       </c>
       <c r="D142" t="n">
-        <v>222.869</v>
+        <v>233.112</v>
       </c>
       <c r="E142" t="n">
-        <v>44.2852</v>
+        <v>52.0842</v>
       </c>
       <c r="F142" t="n">
-        <v>55.1329</v>
+        <v>56.1329</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>47.3903</v>
+        <v>48.5521</v>
       </c>
       <c r="C143" t="n">
-        <v>65.7559</v>
+        <v>65.5795</v>
       </c>
       <c r="D143" t="n">
-        <v>227.042</v>
+        <v>238.058</v>
       </c>
       <c r="E143" t="n">
-        <v>42.2987</v>
+        <v>47.8944</v>
       </c>
       <c r="F143" t="n">
-        <v>54.7062</v>
+        <v>56.8894</v>
       </c>
     </row>
   </sheetData>
